--- a/architectures and decision enablers/architecture decision enabler/swift-threat-assessment/Swift_Security_Assessment.xlsx
+++ b/architectures and decision enablers/architecture decision enabler/swift-threat-assessment/Swift_Security_Assessment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amitp\Documents\portfolio-repo\architectures and decision enablers\architecture decision enabler\swift-threat-assessment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Amit\eBooks\Interview Quick Rampup\Fractional Architect Consulting &amp; Freelancing\UPWORK &amp; TOPMATE FILES AND PRODUCTS\SWIFT_SECURITY_ASSESSMENT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC3E5668-613B-477D-93B3-37357F5C09A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0002D8FF-C24C-4FAD-A14E-96E64FE8AEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{D62D5DFD-F87A-4D1C-B4C2-9718B4BFE1A3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D62D5DFD-F87A-4D1C-B4C2-9718B4BFE1A3}"/>
   </bookViews>
   <sheets>
     <sheet name="User_Responses" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="123">
   <si>
     <t>Category</t>
   </si>
@@ -1863,6 +1863,9 @@
       <t xml:space="preserve">
 </t>
     </r>
+  </si>
+  <si>
+    <t>© 2026 Amit Kulkarni. All rights reserved.</t>
   </si>
 </sst>
 </file>
@@ -2003,7 +2006,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2042,16 +2045,11 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2059,11 +2057,37 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2114,9 +2138,7 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="1"/>
     </dxf>
     <dxf>
       <font>
@@ -2208,7 +2230,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Swift_Security_Assessment.xlsx]Results!PivotTable2</c:name>
+    <c:name>[Swift_Security_Assess.xlsx]Results!PivotTable2</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -3691,8 +3713,8 @@
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{67AED665-9562-40D2-B38F-062B6736059F}" name="Category" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{03F2FCFE-1DC5-4C77-B920-EF0B3618A66A}" name="Client-Specific Question" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{52A3C89F-0892-4359-836A-E4C61F7FF7C1}" name="User Priority" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{49C6DBFA-626B-4C33-9B5E-2F7D83EB221F}" name="User Score" dataDxfId="5">
+    <tableColumn id="3" xr3:uid="{52A3C89F-0892-4359-836A-E4C61F7FF7C1}" name="User Priority" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{49C6DBFA-626B-4C33-9B5E-2F7D83EB221F}" name="User Score" dataDxfId="6">
       <calculatedColumnFormula array="1">_xlfn.SWITCH(C2,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3714,12 +3736,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E2B15CCF-D726-40C5-8B85-899402E9AE03}" name="Table3" displayName="Table3" ref="A1:C5" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E2B15CCF-D726-40C5-8B85-899402E9AE03}" name="Table3" displayName="Table3" ref="A1:C5" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
   <autoFilter ref="A1:C5" xr:uid="{E2B15CCF-D726-40C5-8B85-899402E9AE03}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{957247C0-1F8E-4F1F-BBB9-AB5E4959E43C}" name="States"/>
-    <tableColumn id="2" xr3:uid="{09A551D2-0ADE-4765-8888-B42CA7137A32}" name="Definitions" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{487F9945-FAA7-488D-BFDC-38B5E2BCA065}" name="Operational Impact" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{09A551D2-0ADE-4765-8888-B42CA7137A32}" name="Definitions" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{487F9945-FAA7-488D-BFDC-38B5E2BCA065}" name="Operational Impact" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium24" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4053,10 +4075,10 @@
       <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D2" s="2" cm="1">
+      <c r="D2" s="23" cm="1">
         <f t="array" ref="D2">_xlfn.SWITCH(C2,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.25</v>
       </c>
@@ -4068,12 +4090,12 @@
       <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2" cm="1">
+      <c r="C3" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="23" cm="1">
         <f t="array" ref="D3">_xlfn.SWITCH(C3,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="109.2" x14ac:dyDescent="0.35">
@@ -4083,12 +4105,12 @@
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" s="2" cm="1">
+      <c r="C4" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="23" cm="1">
         <f t="array" ref="D4">_xlfn.SWITCH(C4,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="93.6" x14ac:dyDescent="0.35">
@@ -4098,12 +4120,12 @@
       <c r="B5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D5" s="2" cm="1">
+      <c r="C5" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="23" cm="1">
         <f t="array" ref="D5">_xlfn.SWITCH(C5,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="93.6" x14ac:dyDescent="0.35">
@@ -4113,27 +4135,27 @@
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D6" s="2" cm="1">
+      <c r="C6" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="23" cm="1">
         <f t="array" ref="D6">_xlfn.SWITCH(C6,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="93.6" x14ac:dyDescent="0.3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D7" s="2" cm="1">
+      <c r="C7" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="23" cm="1">
         <f t="array" ref="D7">_xlfn.SWITCH(C7,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="93.6" x14ac:dyDescent="0.3">
@@ -4143,12 +4165,12 @@
       <c r="B8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="2" cm="1">
+      <c r="C8" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="23" cm="1">
         <f t="array" ref="D8">_xlfn.SWITCH(C8,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="93.6" x14ac:dyDescent="0.3">
@@ -4158,10 +4180,10 @@
       <c r="B9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D9" s="2" cm="1">
+      <c r="D9" s="23" cm="1">
         <f t="array" ref="D9">_xlfn.SWITCH(C9,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.25</v>
       </c>
@@ -4173,10 +4195,10 @@
       <c r="B10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="2" cm="1">
+      <c r="D10" s="23" cm="1">
         <f t="array" ref="D10">_xlfn.SWITCH(C10,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -4188,10 +4210,10 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D11" s="2" cm="1">
+      <c r="D11" s="23" cm="1">
         <f t="array" ref="D11">_xlfn.SWITCH(C11,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -4203,27 +4225,27 @@
       <c r="B12" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" s="2" cm="1">
+      <c r="C12" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="23" cm="1">
         <f t="array" ref="D12">_xlfn.SWITCH(C12,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="125.4" x14ac:dyDescent="0.35">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="141" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13" s="2" cm="1">
+      <c r="C13" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="23" cm="1">
         <f t="array" ref="D13">_xlfn.SWITCH(C13,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="109.8" x14ac:dyDescent="0.35">
@@ -4233,12 +4255,12 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14" s="2" cm="1">
+      <c r="C14" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="23" cm="1">
         <f t="array" ref="D14">_xlfn.SWITCH(C14,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="109.8" x14ac:dyDescent="0.35">
@@ -4248,10 +4270,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="2" cm="1">
+      <c r="D15" s="23" cm="1">
         <f t="array" ref="D15">_xlfn.SWITCH(C15,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -4263,10 +4285,10 @@
       <c r="B16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D16" s="2" cm="1">
+      <c r="D16" s="23" cm="1">
         <f t="array" ref="D16">_xlfn.SWITCH(C16,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.25</v>
       </c>
@@ -4278,27 +4300,27 @@
       <c r="B17" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="2" cm="1">
+      <c r="D17" s="23" cm="1">
         <f t="array" ref="D17">_xlfn.SWITCH(C17,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" ht="109.8" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D18" s="2" cm="1">
+      <c r="C18" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="23" cm="1">
         <f t="array" ref="D18">_xlfn.SWITCH(C18,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4308,12 +4330,12 @@
       <c r="B19" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D19" s="2" cm="1">
+      <c r="C19" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="23" cm="1">
         <f t="array" ref="D19">_xlfn.SWITCH(C19,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4323,27 +4345,27 @@
       <c r="B20" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D20" s="2" cm="1">
+      <c r="C20" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="23" cm="1">
         <f t="array" ref="D20">_xlfn.SWITCH(C20,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="109.8" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D21" s="2" cm="1">
+      <c r="C21" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="23" cm="1">
         <f t="array" ref="D21">_xlfn.SWITCH(C21,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4353,10 +4375,10 @@
       <c r="B22" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="2" cm="1">
+      <c r="D22" s="23" cm="1">
         <f t="array" ref="D22">_xlfn.SWITCH(C22,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -4368,10 +4390,10 @@
       <c r="B23" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="2" cm="1">
+      <c r="D23" s="23" cm="1">
         <f t="array" ref="D23">_xlfn.SWITCH(C23,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.25</v>
       </c>
@@ -4383,10 +4405,10 @@
       <c r="B24" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="2" cm="1">
+      <c r="D24" s="23" cm="1">
         <f t="array" ref="D24">_xlfn.SWITCH(C24,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.25</v>
       </c>
@@ -4398,10 +4420,10 @@
       <c r="B25" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D25" s="2" cm="1">
+      <c r="D25" s="23" cm="1">
         <f t="array" ref="D25">_xlfn.SWITCH(C25,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -4413,10 +4435,10 @@
       <c r="B26" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D26" s="2" cm="1">
+      <c r="D26" s="23" cm="1">
         <f t="array" ref="D26">_xlfn.SWITCH(C26,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -4428,10 +4450,10 @@
       <c r="B27" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="D27" s="2" cm="1">
+      <c r="D27" s="23" cm="1">
         <f t="array" ref="D27">_xlfn.SWITCH(C27,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4443,10 +4465,10 @@
       <c r="B28" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="D28" s="2" cm="1">
+      <c r="D28" s="23" cm="1">
         <f t="array" ref="D28">_xlfn.SWITCH(C28,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4458,10 +4480,10 @@
       <c r="B29" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D29" s="2" cm="1">
+      <c r="D29" s="23" cm="1">
         <f t="array" ref="D29">_xlfn.SWITCH(C29,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -4473,10 +4495,10 @@
       <c r="B30" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D30" s="2" cm="1">
+      <c r="D30" s="23" cm="1">
         <f t="array" ref="D30">_xlfn.SWITCH(C30,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -4488,10 +4510,10 @@
       <c r="B31" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D31" s="2" cm="1">
+      <c r="D31" s="23" cm="1">
         <f t="array" ref="D31">_xlfn.SWITCH(C31,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -4503,10 +4525,10 @@
       <c r="B32" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D32" s="2" cm="1">
+      <c r="D32" s="23" cm="1">
         <f t="array" ref="D32">_xlfn.SWITCH(C32,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.25</v>
       </c>
@@ -4518,10 +4540,10 @@
       <c r="B33" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D33" s="2" cm="1">
+      <c r="D33" s="23" cm="1">
         <f t="array" ref="D33">_xlfn.SWITCH(C33,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.25</v>
       </c>
@@ -4533,10 +4555,10 @@
       <c r="B34" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D34" s="2" cm="1">
+      <c r="D34" s="23" cm="1">
         <f t="array" ref="D34">_xlfn.SWITCH(C34,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -4548,10 +4570,10 @@
       <c r="B35" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D35" s="2" cm="1">
+      <c r="D35" s="23" cm="1">
         <f t="array" ref="D35">_xlfn.SWITCH(C35,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -4563,10 +4585,10 @@
       <c r="B36" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="D36" s="2" cm="1">
+      <c r="D36" s="23" cm="1">
         <f t="array" ref="D36">_xlfn.SWITCH(C36,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4578,10 +4600,10 @@
       <c r="B37" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D37" s="2" cm="1">
+      <c r="D37" s="23" cm="1">
         <f t="array" ref="D37">_xlfn.SWITCH(C37,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -4593,10 +4615,10 @@
       <c r="B38" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D38" s="2" cm="1">
+      <c r="D38" s="23" cm="1">
         <f t="array" ref="D38">_xlfn.SWITCH(C38,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -4608,10 +4630,10 @@
       <c r="B39" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D39" s="2" cm="1">
+      <c r="D39" s="23" cm="1">
         <f t="array" ref="D39">_xlfn.SWITCH(C39,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.25</v>
       </c>
@@ -4623,10 +4645,10 @@
       <c r="B40" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D40" s="2" cm="1">
+      <c r="D40" s="23" cm="1">
         <f t="array" ref="D40">_xlfn.SWITCH(C40,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -4638,10 +4660,10 @@
       <c r="B41" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D41" s="2" cm="1">
+      <c r="D41" s="23" cm="1">
         <f t="array" ref="D41">_xlfn.SWITCH(C41,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -4653,10 +4675,10 @@
       <c r="B42" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="D42" s="2" cm="1">
+      <c r="D42" s="23" cm="1">
         <f t="array" ref="D42">_xlfn.SWITCH(C42,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4668,10 +4690,10 @@
       <c r="B43" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="D43" s="2" cm="1">
+      <c r="D43" s="23" cm="1">
         <f t="array" ref="D43">_xlfn.SWITCH(C43,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4683,10 +4705,10 @@
       <c r="B44" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D44" s="2" cm="1">
+      <c r="D44" s="23" cm="1">
         <f t="array" ref="D44">_xlfn.SWITCH(C44,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -4698,10 +4720,10 @@
       <c r="B45" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D45" s="2" cm="1">
+      <c r="D45" s="23" cm="1">
         <f t="array" ref="D45">_xlfn.SWITCH(C45,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -4713,10 +4735,10 @@
       <c r="B46" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D46" s="2" cm="1">
+      <c r="D46" s="23" cm="1">
         <f t="array" ref="D46">_xlfn.SWITCH(C46,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.25</v>
       </c>
@@ -4728,10 +4750,10 @@
       <c r="B47" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D47" s="2" cm="1">
+      <c r="D47" s="23" cm="1">
         <f t="array" ref="D47">_xlfn.SWITCH(C47,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -4743,10 +4765,10 @@
       <c r="B48" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D48" s="2" cm="1">
+      <c r="D48" s="23" cm="1">
         <f t="array" ref="D48">_xlfn.SWITCH(C48,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -4758,10 +4780,10 @@
       <c r="B49" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="D49" s="2" cm="1">
+      <c r="D49" s="23" cm="1">
         <f t="array" ref="D49">_xlfn.SWITCH(C49,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4773,10 +4795,10 @@
       <c r="B50" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="D50" s="2" cm="1">
+      <c r="D50" s="23" cm="1">
         <f t="array" ref="D50">_xlfn.SWITCH(C50,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4788,10 +4810,10 @@
       <c r="B51" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D51" s="2" cm="1">
+      <c r="D51" s="23" cm="1">
         <f t="array" ref="D51">_xlfn.SWITCH(C51,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -4803,10 +4825,10 @@
       <c r="B52" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D52" s="2" cm="1">
+      <c r="D52" s="23" cm="1">
         <f t="array" ref="D52">_xlfn.SWITCH(C52,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -4818,10 +4840,10 @@
       <c r="B53" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D53" s="2" cm="1">
+      <c r="D53" s="23" cm="1">
         <f t="array" ref="D53">_xlfn.SWITCH(C53,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.25</v>
       </c>
@@ -4833,10 +4855,10 @@
       <c r="B54" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D54" s="2" cm="1">
+      <c r="D54" s="23" cm="1">
         <f t="array" ref="D54">_xlfn.SWITCH(C54,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.25</v>
       </c>
@@ -4848,10 +4870,10 @@
       <c r="B55" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D55" s="2" cm="1">
+      <c r="D55" s="23" cm="1">
         <f t="array" ref="D55">_xlfn.SWITCH(C55,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -4863,10 +4885,10 @@
       <c r="B56" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D56" s="2" cm="1">
+      <c r="D56" s="23" cm="1">
         <f t="array" ref="D56">_xlfn.SWITCH(C56,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -4878,10 +4900,10 @@
       <c r="B57" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="D57" s="2" cm="1">
+      <c r="D57" s="23" cm="1">
         <f t="array" ref="D57">_xlfn.SWITCH(C57,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4893,10 +4915,10 @@
       <c r="B58" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="D58" s="2" cm="1">
+      <c r="D58" s="23" cm="1">
         <f t="array" ref="D58">_xlfn.SWITCH(C58,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4908,10 +4930,10 @@
       <c r="B59" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D59" s="2" cm="1">
+      <c r="D59" s="23" cm="1">
         <f t="array" ref="D59">_xlfn.SWITCH(C59,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -4923,10 +4945,10 @@
       <c r="B60" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D60" s="2" cm="1">
+      <c r="D60" s="23" cm="1">
         <f t="array" ref="D60">_xlfn.SWITCH(C60,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -4938,10 +4960,10 @@
       <c r="B61" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D61" s="2" cm="1">
+      <c r="D61" s="23" cm="1">
         <f t="array" ref="D61">_xlfn.SWITCH(C61,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.25</v>
       </c>
@@ -4953,10 +4975,10 @@
       <c r="B62" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D62" s="2" cm="1">
+      <c r="D62" s="23" cm="1">
         <f t="array" ref="D62">_xlfn.SWITCH(C62,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -4968,10 +4990,10 @@
       <c r="B63" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D63" s="2" cm="1">
+      <c r="D63" s="23" cm="1">
         <f t="array" ref="D63">_xlfn.SWITCH(C63,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -4983,10 +5005,10 @@
       <c r="B64" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="D64" s="2" cm="1">
+      <c r="D64" s="23" cm="1">
         <f t="array" ref="D64">_xlfn.SWITCH(C64,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4998,10 +5020,10 @@
       <c r="B65" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="D65" s="2" cm="1">
+      <c r="D65" s="23" cm="1">
         <f t="array" ref="D65">_xlfn.SWITCH(C65,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -5013,10 +5035,10 @@
       <c r="B66" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D66" s="2" cm="1">
+      <c r="D66" s="23" cm="1">
         <f t="array" ref="D66">_xlfn.SWITCH(C66,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -5028,10 +5050,10 @@
       <c r="B67" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D67" s="2" cm="1">
+      <c r="D67" s="23" cm="1">
         <f t="array" ref="D67">_xlfn.SWITCH(C67,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -5043,10 +5065,10 @@
       <c r="B68" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D68" s="2" cm="1">
+      <c r="D68" s="23" cm="1">
         <f t="array" ref="D68">_xlfn.SWITCH(C68,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.25</v>
       </c>
@@ -5058,10 +5080,10 @@
       <c r="B69" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D69" s="2" cm="1">
+      <c r="D69" s="23" cm="1">
         <f t="array" ref="D69">_xlfn.SWITCH(C69,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -5073,10 +5095,10 @@
       <c r="B70" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D70" s="2" cm="1">
+      <c r="D70" s="23" cm="1">
         <f t="array" ref="D70">_xlfn.SWITCH(C70,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -5088,10 +5110,10 @@
       <c r="B71" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="D71" s="2" cm="1">
+      <c r="D71" s="23" cm="1">
         <f t="array" ref="D71">_xlfn.SWITCH(C71,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -5103,10 +5125,10 @@
       <c r="B72" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="D72" s="2" cm="1">
+      <c r="D72" s="23" cm="1">
         <f t="array" ref="D72">_xlfn.SWITCH(C72,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -5118,10 +5140,10 @@
       <c r="B73" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D73" s="2" cm="1">
+      <c r="D73" s="23" cm="1">
         <f t="array" ref="D73">_xlfn.SWITCH(C73,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -5133,10 +5155,10 @@
       <c r="B74" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D74" s="2" cm="1">
+      <c r="D74" s="23" cm="1">
         <f t="array" ref="D74">_xlfn.SWITCH(C74,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -5148,10 +5170,10 @@
       <c r="B75" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D75" s="2" cm="1">
+      <c r="D75" s="23" cm="1">
         <f t="array" ref="D75">_xlfn.SWITCH(C75,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.25</v>
       </c>
@@ -5163,10 +5185,10 @@
       <c r="B76" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D76" s="2" cm="1">
+      <c r="D76" s="23" cm="1">
         <f t="array" ref="D76">_xlfn.SWITCH(C76,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -5178,12 +5200,12 @@
       <c r="B77" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D77" s="2" cm="1">
+      <c r="C77" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="23" cm="1">
         <f t="array" ref="D77">_xlfn.SWITCH(C77,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -5193,18 +5215,24 @@
       <c r="B78" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C78" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D78" s="2" cm="1">
+      <c r="C78" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="D78" s="23" cm="1">
         <f t="array" ref="D78">_xlfn.SWITCH(C78,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>1</v>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A80" s="26" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="81" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C81" s="2"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="8enW3K7gMvXNeomijE3AgI/QQwamCIG6vUkreT9yy++6FrwzfZd9C4p1Zm+FxsKKu/J43Q2Q4/4P4Czindh5AQ==" saltValue="YWDTw57PoUFsz3MPFVvVsQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataValidations xWindow="1284" yWindow="779" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Select Organization Response" prompt="Select 1 out of A,B,C,D" sqref="C2:C78" xr:uid="{38769ACA-BE52-4C22-A94E-0EFE0281E8FE}">
       <formula1>"A,B,C,D"</formula1>
@@ -5219,7 +5247,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6992F667-9237-424C-9FAB-1605BDA91A9B}">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="71.6640625" customWidth="1"/>
@@ -5247,78 +5275,78 @@
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="19">
+      <c r="B2" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$78, A2, User_Responses!$D$2:$D$78)</f>
-        <v>0.7</v>
-      </c>
-      <c r="C2" s="20">
+        <v>0.4</v>
+      </c>
+      <c r="C2" s="18">
         <v>2</v>
       </c>
-      <c r="D2" s="21">
+      <c r="D2" s="24">
         <f>B2*C2</f>
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="19">
+      <c r="B3" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$78, A3, User_Responses!$D$2:$D$78)</f>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="C3" s="20">
+        <v>0.4</v>
+      </c>
+      <c r="C3" s="18">
         <v>3</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D3" s="24">
         <f t="shared" ref="D3:D16" si="0">B3*C3</f>
-        <v>1.6500000000000001</v>
+        <v>1.2000000000000002</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$78, A4, User_Responses!$D$2:$D$78)</f>
-        <v>0.7</v>
-      </c>
-      <c r="C4" s="20">
+        <v>0.45</v>
+      </c>
+      <c r="C4" s="18">
         <v>1</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="24">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$78, A5, User_Responses!$D$2:$D$78)</f>
-        <v>0.8</v>
-      </c>
-      <c r="C5" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="C5" s="18">
         <v>3</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="24">
         <f t="shared" si="0"/>
-        <v>2.4000000000000004</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$78, A6, User_Responses!$D$2:$D$78)</f>
         <v>0.45</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="18">
         <v>2</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="24">
         <f t="shared" si="0"/>
         <v>0.9</v>
       </c>
@@ -5327,14 +5355,14 @@
       <c r="A7" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$78, A7, User_Responses!$D$2:$D$78)</f>
         <v>0.70833333333333337</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="18">
         <v>1</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="24">
         <f t="shared" si="0"/>
         <v>0.70833333333333337</v>
       </c>
@@ -5343,14 +5371,14 @@
       <c r="A8" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$78, A8, User_Responses!$D$2:$D$78)</f>
         <v>0.65</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="18">
         <v>2</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="24">
         <f t="shared" si="0"/>
         <v>1.3</v>
       </c>
@@ -5359,14 +5387,14 @@
       <c r="A9" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$78, A9, User_Responses!$D$2:$D$78)</f>
         <v>0.6</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="18">
         <v>3</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="24">
         <f t="shared" si="0"/>
         <v>1.7999999999999998</v>
       </c>
@@ -5375,14 +5403,14 @@
       <c r="A10" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$78, A10, User_Responses!$D$2:$D$78)</f>
         <v>0.6</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="18">
         <v>3</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="24">
         <f t="shared" si="0"/>
         <v>1.7999999999999998</v>
       </c>
@@ -5391,14 +5419,14 @@
       <c r="A11" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$78, A11, User_Responses!$D$2:$D$78)</f>
         <v>0.8</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="18">
         <v>2</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="24">
         <f t="shared" si="0"/>
         <v>1.6</v>
       </c>
@@ -5407,14 +5435,14 @@
       <c r="A12" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$78, A12, User_Responses!$D$2:$D$78)</f>
         <v>0.55000000000000004</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="18">
         <v>1</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="24">
         <f t="shared" si="0"/>
         <v>0.55000000000000004</v>
       </c>
@@ -5423,14 +5451,14 @@
       <c r="A13" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$78, A13, User_Responses!$D$2:$D$78)</f>
         <v>0.6</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="18">
         <v>3</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="24">
         <f t="shared" si="0"/>
         <v>1.7999999999999998</v>
       </c>
@@ -5439,14 +5467,14 @@
       <c r="A14" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$78, A14, User_Responses!$D$2:$D$78)</f>
         <v>0.8</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="18">
         <v>2</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="24">
         <f t="shared" si="0"/>
         <v>1.6</v>
       </c>
@@ -5455,14 +5483,14 @@
       <c r="A15" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$78, A15, User_Responses!$D$2:$D$78)</f>
         <v>0.7</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="18">
         <v>2</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="24">
         <f t="shared" si="0"/>
         <v>1.4</v>
       </c>
@@ -5471,38 +5499,38 @@
       <c r="A16" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$78, A16, User_Responses!$D$2:$D$78)</f>
-        <v>0.625</v>
-      </c>
-      <c r="C16" s="20">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C16" s="18">
         <v>3</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="24">
         <f t="shared" si="0"/>
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="18" x14ac:dyDescent="0.35">
       <c r="B19" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="27">
         <f>SUM(D2:D16)/SUM(C2:C16)</f>
-        <v>0.65101010101010104</v>
+        <v>0.57676767676767671</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="18" x14ac:dyDescent="0.35">
       <c r="B21" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="7" t="str">
+      <c r="C21" s="28" t="str">
         <f>IF(C19&lt;=40%, "🟢 Optimized Security Posture", IF(C19&lt;=60%, "🟡 Resilient Security Posture", IF(C19&lt;=80%, "🟠 Elevated Exposure Posture", "🔴 Critical Threat Posture")))</f>
-        <v>🟠 Elevated Exposure Posture</v>
+        <v>🟡 Resilient Security Posture</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="16" t="s">
         <v>103</v>
       </c>
       <c r="C25" t="s">
@@ -5513,7 +5541,7 @@
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="17" t="s">
         <v>22</v>
       </c>
       <c r="C26" s="15">
@@ -5524,7 +5552,7 @@
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="17" t="s">
         <v>88</v>
       </c>
       <c r="C27" s="15">
@@ -5535,7 +5563,7 @@
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="17" t="s">
         <v>70</v>
       </c>
       <c r="C28" s="15">
@@ -5546,7 +5574,7 @@
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="17" t="s">
         <v>52</v>
       </c>
       <c r="C29" s="15">
@@ -5557,7 +5585,7 @@
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="17" t="s">
         <v>46</v>
       </c>
       <c r="C30" s="15">
@@ -5568,7 +5596,7 @@
       </c>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="17" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="15">
@@ -5579,7 +5607,7 @@
       </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="17" t="s">
         <v>76</v>
       </c>
       <c r="C32" s="15">
@@ -5589,8 +5617,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B33" s="18" t="s">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B33" s="17" t="s">
         <v>58</v>
       </c>
       <c r="C33" s="15">
@@ -5600,8 +5628,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B34" s="18" t="s">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B34" s="17" t="s">
         <v>4</v>
       </c>
       <c r="C34" s="15">
@@ -5611,8 +5639,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B35" s="18" t="s">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B35" s="17" t="s">
         <v>82</v>
       </c>
       <c r="C35" s="15">
@@ -5622,8 +5650,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B36" s="18" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B36" s="17" t="s">
         <v>40</v>
       </c>
       <c r="C36" s="15">
@@ -5633,8 +5661,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B37" s="18" t="s">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B37" s="17" t="s">
         <v>28</v>
       </c>
       <c r="C37" s="15">
@@ -5644,8 +5672,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B38" s="18" t="s">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B38" s="17" t="s">
         <v>34</v>
       </c>
       <c r="C38" s="15">
@@ -5655,8 +5683,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B39" s="18" t="s">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B39" s="17" t="s">
         <v>17</v>
       </c>
       <c r="C39" s="15">
@@ -5666,8 +5694,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B40" s="18" t="s">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B40" s="17" t="s">
         <v>64</v>
       </c>
       <c r="C40" s="15">
@@ -5677,8 +5705,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B41" s="18" t="s">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B41" s="17" t="s">
         <v>104</v>
       </c>
       <c r="C41" s="15">
@@ -5688,7 +5716,13 @@
         <v>33</v>
       </c>
     </row>
+    <row r="44" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="26" t="s">
+        <v>122</v>
+      </c>
+    </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="Aq8WH8LpBubhez4eteIlWHpr9nZZrFoVeMcBkRVuwe1TYn+9JYOSQAV3pHI76AQ8wYtZ+RoslanTnkgSKjM79g==" saltValue="ub4YSwUAsuWEtUo2yQ/qQQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Select Weight" prompt="Select 1 from (1,2,3,4)" sqref="C2:C16" xr:uid="{C7585D9D-7E7D-4094-AB10-9345EED1BEEF}">
       <formula1>"1,2,3"</formula1>
@@ -5704,7 +5738,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C40AB3C-9D76-48CC-B399-D4A50D69AD7B}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="91.21875" customWidth="1"/>
@@ -5713,24 +5747,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="21" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="19" t="s">
         <v>111</v>
       </c>
       <c r="D2" s="2"/>
@@ -5739,10 +5773,10 @@
       <c r="A3" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="19" t="s">
         <v>114</v>
       </c>
       <c r="D3" s="2"/>
@@ -5751,10 +5785,10 @@
       <c r="A4" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="19" t="s">
         <v>117</v>
       </c>
       <c r="D4" s="2"/>
@@ -5763,15 +5797,21 @@
       <c r="A5" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="19" t="s">
         <v>120</v>
       </c>
       <c r="D5" s="2"/>
     </row>
+    <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="26" t="s">
+        <v>122</v>
+      </c>
+    </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="Z7zIM3dG6z3EyyoqwEVUf2MIaOCnkEjNqmsCyC1DYyFl3ISYG+A6GCatUKUNFW+64rh+2zF6z8Ent4imDBtBCA==" saltValue="8p40nfOyHc+PtVmANFS/mA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
